--- a/ig/DM-AVRIL-2026/ValueSet-jdv-resultat-depistage-hematurie-cisis.xlsx
+++ b/ig/DM-AVRIL-2026/ValueSet-jdv-resultat-depistage-hematurie-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260311144903</t>
+    <t>20260420150250</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:49:03+01:00</t>
+    <t>2026-04-20T15:02:50+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
